--- a/.pic/Labs/lab_13_periph/tab_08.xlsx
+++ b/.pic/Labs/lab_13_periph/tab_08.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\voult\Desktop\APS-reborn\.pic\Labs\lab_13_periph\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA4A29AA-F9FB-4D2B-A839-0354BBC8CFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10620" yWindow="4815" windowWidth="22260" windowHeight="18090" xr2:uid="{C6BDF733-0904-4974-A78F-1E3BFAE70A92}"/>
+    <workbookView xWindow="10620" yWindow="4812" windowWidth="22260" windowHeight="17496"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,9 +33,6 @@
     <t>0x00000000</t>
   </si>
   <si>
-    <t>(RW) диапазон адресов отображаемых символов (char_map)</t>
-  </si>
-  <si>
     <t>…</t>
   </si>
   <si>
@@ -51,34 +42,37 @@
     <t>0x00001000</t>
   </si>
   <si>
-    <t>(RW) диапазон адресов цветовой схемы (color_map)</t>
-  </si>
-  <si>
     <t>0x0000195F</t>
   </si>
   <si>
     <t>0x00002000</t>
   </si>
   <si>
-    <t>(RW) диапазон адресов шрифта для каждого ascii-кода символа</t>
-  </si>
-  <si>
     <t>0x00002FFF</t>
   </si>
   <si>
     <t>0x00003000</t>
   </si>
   <si>
-    <t>не используются</t>
-  </si>
-  <si>
     <t>0xFFFFFFFF</t>
+  </si>
+  <si>
+    <t>(RW) address range of displayed characters (char_map)</t>
+  </si>
+  <si>
+    <t>(RW) address range of the color scheme (color_map)</t>
+  </si>
+  <si>
+    <t>(RW) address range of the font for each ascii character code</t>
+  </si>
+  <si>
+    <t>not used</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -206,40 +200,40 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="20% — акцент3" xfId="1" builtinId="38"/>
+    <cellStyle name="20% - Акцент3" xfId="1" builtinId="38"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -544,100 +538,100 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4B9141-9E9E-4B4E-A51A-3DBD34D58DEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="13"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="13"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B6" s="14"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="B9" s="15"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B10" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="16"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="10"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="10"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="14"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="14"/>
+      <c r="B12" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
